--- a/artfynd/A 69928-2021 artfynd.xlsx
+++ b/artfynd/A 69928-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69928-2021 artfynd.xlsx
+++ b/artfynd/A 69928-2021 artfynd.xlsx
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1141356</v>
+        <v>1156672</v>
       </c>
       <c r="B2" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västra Hungvik, N om sågen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>369152.0380661401</v>
+        <v>369154</v>
       </c>
       <c r="R2" t="n">
-        <v>6608188.579007521</v>
+        <v>6608151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +743,9 @@
           <t>2009-10-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>granskog</t>
+          <t>fuktig granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,50 +777,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1156672</v>
+        <v>1141356</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västra Hungvik, N om sågen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>369153.7551742962</v>
+        <v>369152</v>
       </c>
       <c r="R3" t="n">
-        <v>6608150.511441986</v>
+        <v>6608189</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>2009-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +870,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>fuktig granskog</t>
+          <t>granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
